--- a/data/audit/TagLab_QuickJump_OutlierAudit.xlsx
+++ b/data/audit/TagLab_QuickJump_OutlierAudit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PhD_Data(Large)\06_Final_Analysis\Master_Dataset\OutlierAudit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7272A1D-3639-44F6-806C-C20DB6005E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476A0EB2-932E-4CAF-98D3-CFC34F52A58F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,25 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="72">
   <si>
     <t>TagLab.Genet.Id</t>
   </si>
@@ -231,6 +244,12 @@
   </si>
   <si>
     <t>recruit</t>
+  </si>
+  <si>
+    <t>2022_Single_874</t>
+  </si>
+  <si>
+    <t>2015_Single_1</t>
   </si>
 </sst>
 </file>
@@ -591,7 +610,7 @@
     <col min="4" max="4" width="12.5234375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.1015625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.1015625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7890625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
@@ -701,8 +720,8 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6">
-        <v>0</v>
+      <c r="A6" t="s">
+        <v>70</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -719,8 +738,8 @@
       <c r="F6" t="s">
         <v>61</v>
       </c>
-      <c r="G6">
-        <v>0</v>
+      <c r="G6" t="s">
+        <v>71</v>
       </c>
       <c r="H6">
         <v>128.5</v>
